--- a/data/trans_orig/IP19C08-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP19C08-Provincia-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4150</t>
+          <t>3479</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1368</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7514</t>
+          <t>7357</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>2071</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8951</t>
+          <t>9062</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,77%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15171</t>
+          <t>15842</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19004</t>
+          <t>19161</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25150</t>
+          <t>25222</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>36888</t>
+          <t>36777</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43783</t>
+          <t>43768</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,48%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>620</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5722</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3445</t>
+          <t>2998</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>628</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5901</t>
+          <t>6199</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>51500</t>
+          <t>52037</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>56601</t>
+          <t>56602</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>61530</t>
+          <t>61977</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>116296</t>
+          <t>115998</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>121560</t>
+          <t>121569</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,49%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5450</t>
+          <t>5457</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7556</t>
+          <t>7589</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3144</t>
+          <t>2647</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10127</t>
+          <t>9797</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,07%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28842</t>
+          <t>28835</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27773</t>
+          <t>27740</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34064</t>
+          <t>34063</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>59494</t>
+          <t>59824</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>66477</t>
+          <t>66974</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>96,2%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>1844</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9332</t>
+          <t>9075</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3676</t>
+          <t>4608</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2158</t>
+          <t>2248</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10598</t>
+          <t>10734</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,84%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>32627</t>
+          <t>32884</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>39969</t>
+          <t>40115</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>78,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>37965</t>
+          <t>37033</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>73002</t>
+          <t>72866</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>81442</t>
+          <t>81352</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,31%</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6250</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6385</t>
+          <t>6356</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,06%</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19941</t>
+          <t>20800</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>42274</t>
+          <t>42303</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3862</t>
+          <t>4138</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>4202</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>7,82%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>21478</t>
+          <t>21202</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>48936</t>
+          <t>49496</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2628</t>
+          <t>2632</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10172</t>
+          <t>9413</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2871</t>
+          <t>2792</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11142</t>
+          <t>10521</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6808</t>
+          <t>7199</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>17574</t>
+          <t>17828</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,37%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>55112</t>
+          <t>55871</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>62656</t>
+          <t>62652</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>56887</t>
+          <t>57508</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>65158</t>
+          <t>65237</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>115740</t>
+          <t>115486</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>126506</t>
+          <t>126115</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,6%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>461</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4783</t>
+          <t>4646</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>605</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5339</t>
+          <t>5978</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1782</t>
+          <t>1574</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7780</t>
+          <t>8087</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>76537</t>
+          <t>76674</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>80854</t>
+          <t>80859</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>69074</t>
+          <t>68435</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>73830</t>
+          <t>73808</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>147954</t>
+          <t>147647</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>153952</t>
+          <t>154160</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,99%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>13941</t>
+          <t>13968</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>28110</t>
+          <t>27982</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>11913</t>
+          <t>11336</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>25213</t>
+          <t>24622</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>28943</t>
+          <t>28707</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>50166</t>
+          <t>48048</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>322820</t>
+          <t>322948</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>336989</t>
+          <t>336962</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>336518</t>
+          <t>337109</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>349818</t>
+          <t>350395</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>662495</t>
+          <t>664613</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>683718</t>
+          <t>683954</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,97%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>605</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5417</t>
+          <t>5716</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3183</t>
+          <t>3244</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>624</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6355</t>
+          <t>5934</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>11,4%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16958</t>
+          <t>16659</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21785</t>
+          <t>21770</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>74,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26476</t>
+          <t>26415</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>45679</t>
+          <t>46100</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>51346</t>
+          <t>51410</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4169</t>
+          <t>3116</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4342</t>
+          <t>3697</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>597</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5668</t>
+          <t>5267</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -4512,7 +4512,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>48875</t>
+          <t>49928</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>53290</t>
+          <t>53935</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>105009</t>
+          <t>105410</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>110065</t>
+          <t>110080</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -4747,7 +4747,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4104</t>
+          <t>4108</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>737</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6543</t>
+          <t>7301</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>1492</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8454</t>
+          <t>8104</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29359</t>
+          <t>29355</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32902</t>
+          <t>32144</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38714</t>
+          <t>38708</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>64454</t>
+          <t>64804</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>71432</t>
+          <t>71416</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,95%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>829</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6889</t>
+          <t>6845</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5125,7 +5125,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4451</t>
+          <t>4637</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8803</t>
+          <t>8906</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,73%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>34909</t>
+          <t>34953</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41123</t>
+          <t>40969</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>83,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36775</t>
+          <t>36589</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>74221</t>
+          <t>74118</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>81561</t>
+          <t>81125</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>97,71%</t>
         </is>
       </c>
     </row>
@@ -5468,7 +5468,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3436</t>
+          <t>2762</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5503,7 +5503,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3375</t>
+          <t>3369</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24194</t>
+          <t>24868</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>50323</t>
+          <t>50329</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>463</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4772</t>
+          <t>4826</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>777</t>
+          <t>725</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7371</t>
+          <t>6706</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>2108</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9554</t>
+          <t>9368</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,66%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>30654</t>
+          <t>30600</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>34955</t>
+          <t>34963</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25788</t>
+          <t>26453</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>32382</t>
+          <t>32434</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>59031</t>
+          <t>59217</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>66529</t>
+          <t>66477</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,93%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2341</t>
+          <t>2292</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10589</t>
+          <t>10681</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>665</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>6027</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3639</t>
+          <t>3712</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12872</t>
+          <t>13015</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,92%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>53380</t>
+          <t>53288</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>61628</t>
+          <t>61677</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>62023</t>
+          <t>61137</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>66507</t>
+          <t>66499</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>118261</t>
+          <t>118118</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>127494</t>
+          <t>127421</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,17%</t>
         </is>
       </c>
     </row>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2899</t>
+          <t>3135</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>619</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5786</t>
+          <t>5191</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>630</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7076</t>
+          <t>6616</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>74948</t>
+          <t>74712</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>64301</t>
+          <t>64896</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>69464</t>
+          <t>69468</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>140858</t>
+          <t>141318</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>147166</t>
+          <t>147304</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>9961</t>
+          <t>9148</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>22226</t>
+          <t>21767</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>8242</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>20132</t>
+          <t>20937</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>20456</t>
+          <t>20538</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>37950</t>
+          <t>38228</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>331765</t>
+          <t>332224</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>344030</t>
+          <t>344843</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>345870</t>
+          <t>345065</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>357131</t>
+          <t>357760</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>682043</t>
+          <t>681765</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>699537</t>
+          <t>699455</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,15%</t>
         </is>
       </c>
     </row>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>2163</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3675</t>
+          <t>4098</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>494</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4536</t>
+          <t>4472</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -7492,7 +7492,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25986</t>
+          <t>26403</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26236</t>
+          <t>25813</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>53940</t>
+          <t>54004</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>57970</t>
+          <t>57982</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,16%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>1197</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6766</t>
+          <t>6478</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4098</t>
+          <t>4824</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8366</t>
+          <t>9003</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>46742</t>
+          <t>47030</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>52343</t>
+          <t>52311</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>52635</t>
+          <t>51909</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>101875</t>
+          <t>101238</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>108441</t>
+          <t>108330</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1138</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6718</t>
+          <t>6329</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>659</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5834</t>
+          <t>5819</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9406</t>
+          <t>9825</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39827</t>
+          <t>40216</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>45896</t>
+          <t>45407</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>45169</t>
+          <t>45184</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>50319</t>
+          <t>50344</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>88142</t>
+          <t>87723</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>95577</t>
+          <t>95153</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,54%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8355</t>
+          <t>8490</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5057</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1692</t>
+          <t>1717</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9592</t>
+          <t>9356</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,65%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>31388</t>
+          <t>31253</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>38720</t>
+          <t>38705</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>35513</t>
+          <t>35680</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>70721</t>
+          <t>70957</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>78621</t>
+          <t>78596</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,86%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1331</t>
+          <t>1323</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8269</t>
+          <t>8499</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>1431</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8846</t>
+          <t>8480</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4190</t>
+          <t>4094</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13624</t>
+          <t>13379</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,34%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>59174</t>
+          <t>58944</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>66112</t>
+          <t>66120</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>53097</t>
+          <t>53463</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>59935</t>
+          <t>60512</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>115762</t>
+          <t>116007</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>125196</t>
+          <t>125292</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,84%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8671</t>
+          <t>8625</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>21266</t>
+          <t>21034</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>15297</t>
+          <t>15409</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>16612</t>
+          <t>16379</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>31921</t>
+          <t>31571</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>341352</t>
+          <t>341584</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>353947</t>
+          <t>353993</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>351861</t>
+          <t>351749</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>361856</t>
+          <t>361866</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>697855</t>
+          <t>698205</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>713164</t>
+          <t>713397</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,76%</t>
         </is>
       </c>
     </row>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>549</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5087</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>668</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8020</t>
+          <t>7546</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>1937</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10534</t>
+          <t>10574</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,16%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29731</t>
+          <t>29530</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34340</t>
+          <t>34269</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31845</t>
+          <t>32319</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39166</t>
+          <t>39197</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>64148</t>
+          <t>64108</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>72758</t>
+          <t>72745</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,41%</t>
         </is>
       </c>
     </row>
@@ -11428,7 +11428,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2155</t>
+          <t>1981</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11443,7 +11443,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2592</t>
+          <t>2096</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -11536,7 +11536,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>37897</t>
+          <t>38071</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -11551,7 +11551,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>69282</t>
+          <t>69778</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -11586,7 +11586,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>509</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10634</t>
+          <t>10467</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>551</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10266</t>
+          <t>11374</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>11,21%</t>
         </is>
       </c>
     </row>
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>48027</t>
+          <t>48194</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>58055</t>
+          <t>58152</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>91238</t>
+          <t>90130</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>100980</t>
+          <t>100953</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3788</t>
+          <t>3156</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>578</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4895</t>
+          <t>5547</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12129,7 +12129,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6303</t>
+          <t>6767</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>11,29%</t>
         </is>
       </c>
     </row>
@@ -12187,7 +12187,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21504</t>
+          <t>22136</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -12202,7 +12202,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>29732</t>
+          <t>29080</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34050</t>
+          <t>34049</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>53616</t>
+          <t>53152</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>58973</t>
+          <t>58910</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,32%</t>
         </is>
       </c>
     </row>
@@ -12422,7 +12422,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3427</t>
+          <t>3373</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12437,7 +12437,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12457,7 +12457,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5137</t>
+          <t>4944</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>663</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5535</t>
+          <t>5490</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,18%</t>
         </is>
       </c>
     </row>
@@ -12530,7 +12530,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>23535</t>
+          <t>23589</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -12545,7 +12545,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -12565,7 +12565,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21807</t>
+          <t>22000</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -12580,7 +12580,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>48372</t>
+          <t>48417</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>53236</t>
+          <t>53244</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,77%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>755</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6645</t>
+          <t>6151</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>869</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21078</t>
+          <t>19458</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2769</t>
+          <t>3018</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24166</t>
+          <t>24868</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,34%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>71111</t>
+          <t>71605</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>76996</t>
+          <t>77001</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>87610</t>
+          <t>89230</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>107727</t>
+          <t>107819</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>162278</t>
+          <t>161576</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>183675</t>
+          <t>183426</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,38%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>779</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6799</t>
+          <t>6869</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13143,7 +13143,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2518</t>
+          <t>3575</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>846</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7945</t>
+          <t>7718</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>76496</t>
+          <t>76426</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>82506</t>
+          <t>82516</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,7 +13251,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>99259</t>
+          <t>98202</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>177127</t>
+          <t>177354</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>184204</t>
+          <t>184226</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>4838</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>13992</t>
+          <t>14905</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>9080</t>
+          <t>9516</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>32013</t>
+          <t>32833</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>16461</t>
+          <t>16252</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>39989</t>
+          <t>39753</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>377641</t>
+          <t>376728</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>387084</t>
+          <t>386795</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>452431</t>
+          <t>451611</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>475364</t>
+          <t>474928</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>836087</t>
+          <t>836323</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>859615</t>
+          <t>859824</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,14%</t>
         </is>
       </c>
     </row>
